--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_dn_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_dn_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="inlineStr"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="inlineStr"/>
@@ -812,7 +812,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -905,7 +905,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -998,7 +998,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="inlineStr"/>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>29-01-2021 08:30</t>
+          <t>2021-01-29 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="inlineStr"/>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>23-02-2021 08:30</t>
+          <t>2021-02-23 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="inlineStr"/>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>25-03-2021 08:30</t>
+          <t>2021-03-25 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>01-01-2021 08:30</t>
+          <t>2021-01-01 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1649,7 +1649,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>04-03-2021 08:30</t>
+          <t>2021-04-03 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1742,7 +1742,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="inlineStr"/>
@@ -1835,7 +1835,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2033,7 +2033,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="n">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="n">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>28-09-2021 08:30</t>
+          <t>2021-09-28 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="n">
